--- a/documents/HOWTO/928/Comprehensive_S4_bolt_lengths_and_torque_values.xlsx
+++ b/documents/HOWTO/928/Comprehensive_S4_bolt_lengths_and_torque_values.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mike\MyGarage\Porsche_928\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B579BD0-3FB0-4426-B757-46FFE123DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FB29DE-B55D-41BE-9375-BC41BE8CC4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41E7AFCC-C221-4A24-86B9-24819EE2B171}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Specs" sheetId="1" r:id="rId1"/>
     <sheet name="ReadMe" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Specs!$A$1:$E$287</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="432">
   <si>
     <t>ENGINE BLOCK PROPER</t>
   </si>
@@ -127,9 +128,6 @@
   </si>
   <si>
     <t>Front fuel damper 928.110.202.01 0 280 161 034</t>
-  </si>
-  <si>
-    <t>Z-shpaed bracket, A17 washer, then M16 x 1.5 hex nut</t>
   </si>
   <si>
     <t>left rear damper</t>
@@ -901,9 +899,6 @@
     <t>900-067-276-01</t>
   </si>
   <si>
-    <t>Temp II sensor to water crossover Bosch (0280130069)</t>
-  </si>
-  <si>
     <t>928-606-149-00</t>
   </si>
   <si>
@@ -1324,9 +1319,6 @@
     <t xml:space="preserve">Airbox 10mm nuts M6 </t>
   </si>
   <si>
-    <t>Intake temp senor into top-rear of intake 22 mm deep socket (Wahler)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Flappy vacuum actuator mouting bolts M6 x 16 </t>
   </si>
   <si>
@@ -1424,6 +1416,15 @@
   </si>
   <si>
     <t xml:space="preserve">Camshaft bearing saddles to cylinder head, XZN bolts M8 x 35 </t>
+  </si>
+  <si>
+    <t>Z-shaed bracket, A17 washer, then M16 x 1.5 hex nut</t>
+  </si>
+  <si>
+    <t>Temp II sensor to water crossover Bosch (0280130069) same as in Intake Manifold section</t>
+  </si>
+  <si>
+    <t>Intake temp senor into top-rear of intake 22 mm deep socket (Wahler) (estimate, exact value is not found)</t>
   </si>
 </sst>
 </file>
@@ -1725,6 +1726,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1734,15 +1795,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1752,59 +1804,8 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2213,33 +2214,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CE7A37-085A-4F02-A826-18FEACF4E97A}">
   <dimension ref="A1:H286"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="76.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="5"/>
-    <col min="5" max="5" width="31.85546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="100.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="5"/>
+    <col min="5" max="5" width="31.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>192</v>
-      </c>
       <c r="D1" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="62" t="s">
         <v>0</v>
       </c>
@@ -2247,354 +2248,354 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="63"/>
       <c r="B3" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.35">
       <c r="A4" s="63"/>
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="63"/>
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="63"/>
       <c r="B6" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="63"/>
       <c r="B7" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D7" s="5">
         <v>2</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="63"/>
       <c r="B8" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D8" s="5">
         <v>3</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="63"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="63"/>
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="63"/>
       <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="63"/>
       <c r="B12" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="63"/>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="7"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="63"/>
       <c r="B14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="63"/>
       <c r="B15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="63"/>
       <c r="B16" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D16" s="5">
         <v>2</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="63"/>
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E17" s="7"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="63"/>
       <c r="B18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="63"/>
       <c r="B19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="7"/>
     </row>
-    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="63"/>
       <c r="B20" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D20" s="5">
         <v>2</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="63"/>
       <c r="B21" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D21" s="5">
         <v>25</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="63"/>
       <c r="B22" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D22" s="5">
         <v>5</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="63"/>
       <c r="B23" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E23" s="7"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="63"/>
       <c r="B24" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="7"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="63"/>
       <c r="B25" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="63"/>
       <c r="B26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="7"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="63"/>
       <c r="B27" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="63"/>
       <c r="B28" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="63"/>
       <c r="B29" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="63"/>
       <c r="B30" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E30" s="7"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="63"/>
       <c r="B31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="63"/>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="63"/>
       <c r="B33" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>363</v>
-      </c>
       <c r="E33" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="64"/>
       <c r="B34" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D34" s="11">
         <v>3</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="65" t="s">
         <v>16</v>
       </c>
@@ -2605,104 +2606,104 @@
       <c r="D35" s="2"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="66"/>
       <c r="B36" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D36" s="5">
         <v>1</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="66"/>
       <c r="B37" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="66"/>
       <c r="B38" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D38" s="5">
         <v>1</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="66"/>
       <c r="B39" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D39" s="5">
         <v>1</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="66"/>
       <c r="B40" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D40" s="5">
         <v>1</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="66"/>
       <c r="B41" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="66"/>
       <c r="B42" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D42" s="5">
         <v>2</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="67"/>
       <c r="B43" s="10" t="s">
         <v>18</v>
@@ -2711,2400 +2712,2402 @@
       <c r="D43" s="11"/>
       <c r="E43" s="12"/>
     </row>
-    <row r="44" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="68" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D44" s="5">
         <v>18</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="69"/>
       <c r="B45" s="4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="69"/>
       <c r="B46" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D46" s="5">
         <v>52</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="69"/>
       <c r="B47" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D47" s="5">
         <v>5</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="69"/>
       <c r="B48" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E48" s="7"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="69"/>
       <c r="B49" s="4" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D49" s="5">
         <v>2</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" s="69"/>
       <c r="B50" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="69"/>
       <c r="B51" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E51" s="7"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="69"/>
       <c r="B52" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E52" s="7"/>
     </row>
-    <row r="53" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="69"/>
       <c r="B53" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="69"/>
       <c r="B54" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D54" s="5">
         <v>8</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="69"/>
       <c r="B55" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="69"/>
       <c r="B56" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D56" s="5">
         <v>1</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="69"/>
       <c r="B57" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D57" s="5">
         <v>2</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="69"/>
       <c r="B58" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="7"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="69"/>
       <c r="B59" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>284</v>
       </c>
       <c r="D59" s="5">
         <v>2</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="69"/>
       <c r="B60" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D60" s="5">
         <v>2</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="69"/>
       <c r="B61" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D61" s="11">
         <v>1</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="70" t="s">
         <v>21</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D62" s="5">
         <v>16</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="71"/>
       <c r="B63" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D63" s="5">
         <v>2</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="71"/>
       <c r="B64" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="71"/>
       <c r="B65" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="71"/>
       <c r="B66" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="71"/>
       <c r="B67" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E67" s="7"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="71"/>
       <c r="B68" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D68" s="5">
         <v>10</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="71"/>
       <c r="B69" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D69" s="5">
         <v>4</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="71"/>
       <c r="B70" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E70" s="7"/>
     </row>
-    <row r="71" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="71"/>
       <c r="B71" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D71" s="5">
         <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="71"/>
       <c r="B72" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D72" s="5">
         <v>2</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="71"/>
       <c r="B73" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D73" s="5">
         <v>2</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="71"/>
       <c r="B74" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D74" s="5">
         <v>2</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="71"/>
       <c r="B75" s="4" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D75" s="5">
         <v>1</v>
       </c>
-      <c r="E75" s="7"/>
-    </row>
-    <row r="76" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E75" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="71"/>
       <c r="B76" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="D76" s="5">
         <v>4</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="71"/>
       <c r="B77" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="D77" s="5">
         <v>4</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="71"/>
       <c r="B78" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D78" s="5">
         <v>4</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="71"/>
       <c r="B79" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E79" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="E79" s="14" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="71"/>
       <c r="B80" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E80" s="7"/>
     </row>
-    <row r="81" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="71"/>
       <c r="B81" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>264</v>
-      </c>
       <c r="E81" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="71"/>
       <c r="B82" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D82" s="5">
         <v>3</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="71"/>
       <c r="B83" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D83" s="5">
         <v>10</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="71"/>
       <c r="B84" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E84" s="7"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="71"/>
       <c r="B85" s="4" t="s">
-        <v>28</v>
+        <v>429</v>
       </c>
       <c r="E85" s="7"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="71"/>
       <c r="B86" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E86" s="7"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="71"/>
       <c r="B87" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E87" s="7"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="71"/>
       <c r="B88" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E88" s="7"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="72"/>
       <c r="B89" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
       <c r="E89" s="12"/>
     </row>
-    <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D90" s="5">
         <v>2</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="60"/>
       <c r="B91" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D91" s="5">
         <v>3</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="60"/>
       <c r="B92" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E92" s="7"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="60"/>
       <c r="B93" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E93" s="7"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="60"/>
       <c r="B94" s="4" t="s">
-        <v>270</v>
+        <v>430</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D94" s="5">
         <v>1</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="60"/>
       <c r="B95" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E95" s="7"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="60"/>
       <c r="B96" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E96" s="7"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="60"/>
       <c r="B97" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E97" s="7"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="60"/>
       <c r="B98" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E98" s="7"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="60"/>
       <c r="B99" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="60"/>
       <c r="B100" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C100" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="61"/>
       <c r="B101" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D101" s="11">
         <v>2</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="49" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E102" s="7"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="50"/>
       <c r="B103" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E103" s="7"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="50"/>
       <c r="B104" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E104" s="7"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="50"/>
       <c r="B105" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E105" s="7"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="50"/>
       <c r="B106" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E106" s="7"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="50"/>
       <c r="B107" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E107" s="7"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="50"/>
       <c r="B108" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E108" s="7"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="50"/>
       <c r="B109" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E109" s="7"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="50"/>
       <c r="B110" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E110" s="7"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="50"/>
       <c r="B111" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E111" s="7"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="50"/>
       <c r="B112" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E112" s="7"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="50"/>
       <c r="B113" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E113" s="7"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="50"/>
       <c r="B114" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E114" s="7"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="51"/>
       <c r="B115" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C115" s="11"/>
       <c r="D115" s="11"/>
       <c r="E115" s="12"/>
     </row>
-    <row r="116" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D116" s="20">
         <v>2</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="53"/>
       <c r="B117" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D117" s="5">
         <v>1</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="53"/>
       <c r="B118" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D118" s="5">
         <v>1</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="53"/>
       <c r="B119" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D119" s="5">
         <v>1</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="53"/>
       <c r="B120" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D120" s="5">
         <v>5</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="54"/>
       <c r="B121" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C121" s="11"/>
       <c r="D121" s="11"/>
       <c r="E121" s="12"/>
     </row>
-    <row r="122" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D122" s="20">
         <v>2</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="56"/>
       <c r="B123" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D123" s="11">
         <v>2</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="46" t="s">
-        <v>225</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="32" t="s">
+        <v>224</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D124" s="5">
         <v>1</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="32"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="33"/>
       <c r="B125" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D125" s="5">
         <v>2</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="32"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="33"/>
       <c r="B126" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D126" s="11">
         <v>3</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="57" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D127" s="5">
         <v>1</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="58"/>
       <c r="B128" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D128" s="5">
         <v>1</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="58"/>
       <c r="B129" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D129" s="5">
         <v>1</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="58"/>
       <c r="B130" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D130" s="5">
         <v>1</v>
       </c>
       <c r="E130" s="7"/>
     </row>
-    <row r="131" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="58"/>
       <c r="B131" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D131" s="11">
         <v>1</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="40" t="s">
-        <v>227</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A132" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D132" s="5">
         <v>5</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="26"/>
       <c r="B133" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="26"/>
       <c r="B134" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D134" s="5">
         <v>5</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="26"/>
       <c r="B135" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D135" s="5">
         <v>1</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="26"/>
       <c r="B136" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D136" s="5">
         <v>2</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="26"/>
       <c r="B137" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C137" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="D137" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="D137" s="19" t="s">
-        <v>307</v>
-      </c>
       <c r="E137" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="37" t="s">
-        <v>232</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="22" t="s">
+        <v>231</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D138" s="5">
         <v>2</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="38"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="23"/>
       <c r="B139" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D139" s="5">
         <v>2</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="38"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="23"/>
       <c r="B140" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D140" s="5">
         <v>1</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="39"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="24"/>
       <c r="B141" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D141" s="11">
         <v>4</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="34" t="s">
-        <v>231</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="48" t="s">
+        <v>230</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D142" s="5">
         <v>4</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="35"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="36"/>
       <c r="B143" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D143" s="5">
         <v>4</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="36"/>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="37"/>
       <c r="B144" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D144" s="11">
         <v>4</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="31" t="s">
-        <v>233</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="41" t="s">
+        <v>232</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E145" s="7"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="32"/>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" s="33"/>
       <c r="B146" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E146" s="7"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="32"/>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" s="33"/>
       <c r="B147" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E147" s="7"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="33"/>
+      <c r="B148" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E147" s="7"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="32"/>
-      <c r="B148" s="4" t="s">
+      <c r="E148" s="7"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="33"/>
+      <c r="B149" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E149" s="7"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="33"/>
+      <c r="B150" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E148" s="7"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="32"/>
-      <c r="B149" s="4" t="s">
+      <c r="E150" s="7"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="33"/>
+      <c r="B151" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E149" s="7"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="32"/>
-      <c r="B150" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E150" s="7"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="32"/>
-      <c r="B151" s="4" t="s">
+      <c r="E151" s="7"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" s="33"/>
+      <c r="B152" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E151" s="7"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="32"/>
-      <c r="B152" s="4" t="s">
+      <c r="E152" s="7"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" s="33"/>
+      <c r="B153" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E152" s="7"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="32"/>
-      <c r="B153" s="4" t="s">
+      <c r="E153" s="7"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" s="33"/>
+      <c r="B154" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E153" s="7"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="32"/>
-      <c r="B154" s="4" t="s">
+      <c r="E154" s="7"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" s="33"/>
+      <c r="B155" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E154" s="7"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="32"/>
-      <c r="B155" s="4" t="s">
+      <c r="E155" s="7"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" s="34"/>
+      <c r="B156" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="E155" s="7"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="33"/>
-      <c r="B156" s="10" t="s">
-        <v>106</v>
       </c>
       <c r="C156" s="11"/>
       <c r="D156" s="11"/>
       <c r="E156" s="12"/>
     </row>
-    <row r="157" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="28" t="s">
-        <v>234</v>
+    <row r="157" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="45" t="s">
+        <v>233</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D157" s="5">
         <v>2</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="29"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="46"/>
       <c r="B158" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D158" s="5">
         <v>2</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="30"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="47"/>
       <c r="B159" s="10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C159" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D159" s="11">
         <v>6</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="25" t="s">
-        <v>54</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="39" t="s">
+        <v>53</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E160" s="21" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="26"/>
       <c r="B161" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C161" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="C161" s="9" t="s">
-        <v>318</v>
       </c>
       <c r="D161" s="5">
         <v>8</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="26"/>
       <c r="B162" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E162" s="7"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="26"/>
       <c r="B163" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E163" s="7"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="26"/>
       <c r="B164" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E164" s="7"/>
     </row>
-    <row r="165" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="26"/>
       <c r="B165" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D165" s="5">
         <v>6</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="26"/>
       <c r="B166" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E166" s="7"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="26"/>
       <c r="B167" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E167" s="7"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A168" s="40"/>
+      <c r="B168" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="E167" s="7"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="27"/>
-      <c r="B168" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="C168" s="11"/>
       <c r="D168" s="11"/>
       <c r="E168" s="12"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="22" t="s">
-        <v>235</v>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A169" s="42" t="s">
+        <v>234</v>
       </c>
       <c r="B169" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E169" s="7"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A170" s="43"/>
+      <c r="B170" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E169" s="7"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="23"/>
-      <c r="B170" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="E170" s="7"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="23"/>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A171" s="43"/>
       <c r="B171" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E171" s="7"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A172" s="44"/>
+      <c r="B172" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="E171" s="7"/>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="24"/>
-      <c r="B172" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="C172" s="11"/>
       <c r="D172" s="11"/>
       <c r="E172" s="12"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="47" t="s">
-        <v>236</v>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A173" s="35" t="s">
+        <v>235</v>
       </c>
       <c r="B173" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E173" s="7"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A174" s="36"/>
+      <c r="B174" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E173" s="7"/>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="35"/>
-      <c r="B174" s="4" t="s">
+      <c r="E174" s="7"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A175" s="36"/>
+      <c r="B175" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E174" s="7"/>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="35"/>
-      <c r="B175" s="4" t="s">
+      <c r="E175" s="7"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A176" s="36"/>
+      <c r="B176" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E175" s="7"/>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="35"/>
-      <c r="B176" s="4" t="s">
+      <c r="E176" s="7"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A177" s="36"/>
+      <c r="B177" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E176" s="7"/>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="35"/>
-      <c r="B177" s="4" t="s">
+      <c r="E177" s="7"/>
+    </row>
+    <row r="178" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A178" s="36"/>
+      <c r="B178" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E177" s="7"/>
-    </row>
-    <row r="178" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="35"/>
-      <c r="B178" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="C178" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D178" s="5">
         <v>12</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="35"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A179" s="36"/>
       <c r="B179" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E179" s="7"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A180" s="36"/>
+      <c r="B180" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E179" s="7"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="35"/>
-      <c r="B180" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="C180" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D180" s="5">
         <v>7</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="35"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A181" s="36"/>
       <c r="B181" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E181" s="7"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="35"/>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A182" s="36"/>
       <c r="B182" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D182" s="5">
         <v>2</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="35"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A183" s="36"/>
       <c r="B183" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D183" s="5">
         <v>2</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A184" s="35"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A184" s="36"/>
       <c r="B184" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D184" s="5">
         <v>12</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="35"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A185" s="36"/>
       <c r="B185" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E185" s="7"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A186" s="36"/>
+      <c r="B186" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E186" s="7"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A187" s="36"/>
+      <c r="B187" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E187" s="7"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A188" s="36"/>
+      <c r="B188" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E188" s="7"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A189" s="36"/>
+      <c r="B189" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E189" s="7"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A190" s="36"/>
+      <c r="B190" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E190" s="7"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A191" s="36"/>
+      <c r="B191" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E185" s="7"/>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="35"/>
-      <c r="B186" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E186" s="7"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="35"/>
-      <c r="B187" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E187" s="7"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="35"/>
-      <c r="B188" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E188" s="7"/>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="35"/>
-      <c r="B189" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E189" s="7"/>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="35"/>
-      <c r="B190" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E190" s="7"/>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="35"/>
-      <c r="B191" s="4" t="s">
+      <c r="E191" s="7"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A192" s="37"/>
+      <c r="B192" s="10" t="s">
         <v>59</v>
-      </c>
-      <c r="E191" s="7"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="36"/>
-      <c r="B192" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="C192" s="11"/>
       <c r="D192" s="11"/>
       <c r="E192" s="12"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="31" t="s">
-        <v>229</v>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A193" s="41" t="s">
+        <v>228</v>
       </c>
       <c r="B193" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E193" s="7"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A194" s="33"/>
+      <c r="B194" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E194" s="7"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A195" s="33"/>
+      <c r="B195" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E195" s="7"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A196" s="33"/>
+      <c r="B196" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E193" s="7"/>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" s="32"/>
-      <c r="B194" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E194" s="7"/>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" s="32"/>
-      <c r="B195" s="4" t="s">
+      <c r="E196" s="7"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A197" s="33"/>
+      <c r="B197" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E195" s="7"/>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" s="32"/>
-      <c r="B196" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E196" s="7"/>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="32"/>
-      <c r="B197" s="4" t="s">
+      <c r="E197" s="7"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A198" s="33"/>
+      <c r="B198" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E197" s="7"/>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" s="32"/>
-      <c r="B198" s="4" t="s">
+      <c r="E198" s="7"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A199" s="33"/>
+      <c r="B199" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E198" s="7"/>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" s="32"/>
-      <c r="B199" s="4" t="s">
+      <c r="E199" s="7"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A200" s="33"/>
+      <c r="B200" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E199" s="7"/>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" s="32"/>
-      <c r="B200" s="4" t="s">
+      <c r="E200" s="7"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A201" s="33"/>
+      <c r="B201" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E200" s="7"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" s="32"/>
-      <c r="B201" s="4" t="s">
+      <c r="E201" s="7"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A202" s="33"/>
+      <c r="B202" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E201" s="7"/>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" s="32"/>
-      <c r="B202" s="4" t="s">
+      <c r="E202" s="7"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A203" s="33"/>
+      <c r="B203" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E202" s="7"/>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" s="32"/>
-      <c r="B203" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="E203" s="7"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" s="33"/>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A204" s="34"/>
       <c r="B204" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="11"/>
       <c r="E204" s="12"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" s="43" t="s">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A205" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E205" s="7"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A206" s="30"/>
+      <c r="B206" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E206" s="7"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A207" s="30"/>
+      <c r="B207" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E207" s="7"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A208" s="30"/>
+      <c r="B208" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E208" s="7"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A209" s="30"/>
+      <c r="B209" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E209" s="7"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A210" s="30"/>
+      <c r="B210" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E210" s="7"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211" s="30"/>
+      <c r="B211" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E211" s="7"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A212" s="30"/>
+      <c r="B212" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E212" s="7"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A213" s="30"/>
+      <c r="B213" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E213" s="7"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A214" s="30"/>
+      <c r="B214" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E214" s="7"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215" s="30"/>
+      <c r="B215" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E215" s="7"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216" s="30"/>
+      <c r="B216" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E216" s="7"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217" s="30"/>
+      <c r="B217" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E217" s="7"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" s="30"/>
+      <c r="B218" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E218" s="7"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" s="30"/>
+      <c r="B219" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E219" s="7"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A220" s="30"/>
+      <c r="B220" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E220" s="7"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A221" s="30"/>
+      <c r="B221" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E221" s="7"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A222" s="30"/>
+      <c r="B222" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E222" s="7"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" s="30"/>
+      <c r="B223" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B205" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E205" s="7"/>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" s="44"/>
-      <c r="B206" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E206" s="7"/>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" s="44"/>
-      <c r="B207" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E207" s="7"/>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" s="44"/>
-      <c r="B208" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E208" s="7"/>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="44"/>
-      <c r="B209" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E209" s="7"/>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="44"/>
-      <c r="B210" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E210" s="7"/>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="44"/>
-      <c r="B211" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E211" s="7"/>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="44"/>
-      <c r="B212" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E212" s="7"/>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="44"/>
-      <c r="B213" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E213" s="7"/>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="44"/>
-      <c r="B214" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E214" s="7"/>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="44"/>
-      <c r="B215" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E215" s="7"/>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="44"/>
-      <c r="B216" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E216" s="7"/>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="44"/>
-      <c r="B217" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E217" s="7"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="44"/>
-      <c r="B218" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E218" s="7"/>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="44"/>
-      <c r="B219" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E219" s="7"/>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="44"/>
-      <c r="B220" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E220" s="7"/>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="44"/>
-      <c r="B221" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E221" s="7"/>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="44"/>
-      <c r="B222" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E222" s="7"/>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="44"/>
-      <c r="B223" s="4" t="s">
+      <c r="E223" s="7"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" s="30"/>
+      <c r="B224" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E223" s="7"/>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="44"/>
-      <c r="B224" s="4" t="s">
+      <c r="E224" s="7"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" s="30"/>
+      <c r="B225" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E224" s="7"/>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" s="44"/>
-      <c r="B225" s="4" t="s">
+      <c r="E225" s="7"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A226" s="30"/>
+      <c r="B226" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E225" s="7"/>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" s="44"/>
-      <c r="B226" s="4" t="s">
+      <c r="E226" s="7"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A227" s="30"/>
+      <c r="B227" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E226" s="7"/>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" s="44"/>
-      <c r="B227" s="4" t="s">
+      <c r="E227" s="7"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A228" s="30"/>
+      <c r="B228" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E227" s="7"/>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A228" s="44"/>
-      <c r="B228" s="4" t="s">
+      <c r="E228" s="7"/>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A229" s="31"/>
+      <c r="B229" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="E228" s="7"/>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" s="45"/>
-      <c r="B229" s="10" t="s">
-        <v>69</v>
       </c>
       <c r="C229" s="11"/>
       <c r="D229" s="11"/>
       <c r="E229" s="12"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A230" s="25" t="s">
-        <v>230</v>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A230" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E230" s="7"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="26"/>
       <c r="B231" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E231" s="7"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="26"/>
       <c r="B232" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E232" s="7"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="26"/>
       <c r="B233" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E233" s="7"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="26"/>
       <c r="B234" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E234" s="7"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="26"/>
       <c r="B235" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E235" s="7"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="26"/>
       <c r="B236" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E236" s="7"/>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="26"/>
       <c r="B237" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E237" s="7"/>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="26"/>
       <c r="B238" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E238" s="7"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="26"/>
       <c r="B239" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E239" s="7"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" s="40"/>
+      <c r="B240" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="E239" s="7"/>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="27"/>
-      <c r="B240" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="C240" s="11"/>
       <c r="D240" s="11"/>
       <c r="E240" s="12"/>
     </row>
-    <row r="241" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A241" s="48" t="s">
-        <v>71</v>
+    <row r="241" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A241" s="38" t="s">
+        <v>70</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D241" s="5">
         <v>2</v>
       </c>
       <c r="E241" s="7"/>
     </row>
-    <row r="242" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A242" s="38"/>
+    <row r="242" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A242" s="23"/>
       <c r="B242" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D242" s="5">
         <v>4</v>
       </c>
       <c r="E242" s="7"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="38"/>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A243" s="23"/>
       <c r="B243" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E243" s="7"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A244" s="23"/>
+      <c r="B244" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E243" s="7"/>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" s="38"/>
-      <c r="B244" s="4" t="s">
+      <c r="E244" s="7"/>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A245" s="23"/>
+      <c r="B245" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E245" s="7"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A246" s="24"/>
+      <c r="B246" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="E244" s="7"/>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="38"/>
-      <c r="B245" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E245" s="7"/>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" s="39"/>
-      <c r="B246" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="C246" s="11"/>
       <c r="D246" s="11"/>
       <c r="E246" s="12"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" s="47" t="s">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A247" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E247" s="7"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A248" s="36"/>
+      <c r="B248" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="E248" s="7"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A249" s="36"/>
+      <c r="B249" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E249" s="7"/>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A250" s="36"/>
+      <c r="B250" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E250" s="7"/>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A251" s="36"/>
+      <c r="B251" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E251" s="7"/>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A252" s="36"/>
+      <c r="B252" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E252" s="7"/>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A253" s="36"/>
+      <c r="B253" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E253" s="7"/>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A254" s="36"/>
+      <c r="B254" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E247" s="7"/>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" s="35"/>
-      <c r="B248" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E248" s="7"/>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" s="35"/>
-      <c r="B249" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E249" s="7"/>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" s="35"/>
-      <c r="B250" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E250" s="7"/>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" s="35"/>
-      <c r="B251" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E251" s="7"/>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" s="35"/>
-      <c r="B252" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E252" s="7"/>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" s="35"/>
-      <c r="B253" s="4" t="s">
+      <c r="E254" s="7"/>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A255" s="36"/>
+      <c r="B255" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E255" s="7"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A256" s="36"/>
+      <c r="B256" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E253" s="7"/>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" s="35"/>
-      <c r="B254" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E254" s="7"/>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" s="35"/>
-      <c r="B255" s="4" t="s">
+      <c r="E256" s="7"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A257" s="36"/>
+      <c r="B257" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E257" s="7"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A258" s="36"/>
+      <c r="B258" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E258" s="7"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A259" s="36"/>
+      <c r="B259" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E255" s="7"/>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="35"/>
-      <c r="B256" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E256" s="7"/>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="35"/>
-      <c r="B257" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E257" s="7"/>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="35"/>
-      <c r="B258" s="4" t="s">
+      <c r="E259" s="7"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A260" s="36"/>
+      <c r="B260" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E260" s="7"/>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" s="36"/>
+      <c r="B261" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E261" s="7"/>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A262" s="36"/>
+      <c r="B262" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E262" s="7"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A263" s="36"/>
+      <c r="B263" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E263" s="7"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A264" s="36"/>
+      <c r="B264" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E264" s="7"/>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A265" s="36"/>
+      <c r="B265" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E265" s="7"/>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A266" s="36"/>
+      <c r="B266" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E266" s="7"/>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A267" s="36"/>
+      <c r="B267" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E267" s="7"/>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A268" s="36"/>
+      <c r="B268" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E268" s="7"/>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A269" s="36"/>
+      <c r="B269" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E269" s="7"/>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A270" s="36"/>
+      <c r="B270" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E270" s="7"/>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A271" s="36"/>
+      <c r="B271" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E258" s="7"/>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="35"/>
-      <c r="B259" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E259" s="7"/>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="35"/>
-      <c r="B260" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E260" s="7"/>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="35"/>
-      <c r="B261" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E261" s="7"/>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="35"/>
-      <c r="B262" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E262" s="7"/>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="35"/>
-      <c r="B263" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E263" s="7"/>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="35"/>
-      <c r="B264" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E264" s="7"/>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="35"/>
-      <c r="B265" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E265" s="7"/>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="35"/>
-      <c r="B266" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E266" s="7"/>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="35"/>
-      <c r="B267" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E267" s="7"/>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="35"/>
-      <c r="B268" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E268" s="7"/>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="35"/>
-      <c r="B269" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E269" s="7"/>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="35"/>
-      <c r="B270" s="4" t="s">
+      <c r="E271" s="7"/>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A272" s="36"/>
+      <c r="B272" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E272" s="7"/>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A273" s="37"/>
+      <c r="B273" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="E270" s="7"/>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="35"/>
-      <c r="B271" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E271" s="7"/>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="35"/>
-      <c r="B272" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E272" s="7"/>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" s="36"/>
-      <c r="B273" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="C273" s="11"/>
       <c r="D273" s="11"/>
       <c r="E273" s="12"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" s="46" t="s">
-        <v>237</v>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A274" s="32" t="s">
+        <v>236</v>
       </c>
       <c r="B274" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E274" s="7"/>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A275" s="33"/>
+      <c r="B275" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E275" s="7"/>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A276" s="33"/>
+      <c r="B276" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E274" s="7"/>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" s="32"/>
-      <c r="B275" s="4" t="s">
+      <c r="E276" s="7"/>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A277" s="33"/>
+      <c r="B277" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E275" s="7"/>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A276" s="32"/>
-      <c r="B276" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E276" s="7"/>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A277" s="32"/>
-      <c r="B277" s="4" t="s">
+      <c r="E277" s="7"/>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A278" s="34"/>
+      <c r="B278" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="E277" s="7"/>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A278" s="33"/>
-      <c r="B278" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="C278" s="11"/>
       <c r="D278" s="11"/>
       <c r="E278" s="12"/>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A279" s="43" t="s">
-        <v>86</v>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A279" s="29" t="s">
+        <v>85</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D279" s="5">
         <v>4</v>
       </c>
       <c r="E279" s="14" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A280" s="44"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A280" s="30"/>
       <c r="B280" s="4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D280" s="5">
         <v>6</v>
       </c>
       <c r="E280" s="7"/>
     </row>
-    <row r="281" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A281" s="45"/>
+    <row r="281" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A281" s="31"/>
       <c r="B281" s="10" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C281" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D281" s="11">
         <v>1</v>
       </c>
       <c r="E281" s="12"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A282" s="41" t="s">
-        <v>238</v>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A282" s="27" t="s">
+        <v>237</v>
       </c>
       <c r="B282" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E282" s="7"/>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A283" s="28"/>
+      <c r="B283" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E282" s="7"/>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A283" s="42"/>
-      <c r="B283" s="4" t="s">
+      <c r="E283" s="7"/>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A284" s="28"/>
+      <c r="B284" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E283" s="7"/>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A284" s="42"/>
-      <c r="B284" s="4" t="s">
+      <c r="E284" s="7"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A285" s="28"/>
+      <c r="B285" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E284" s="7"/>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A285" s="42"/>
-      <c r="B285" s="4" t="s">
+      <c r="E285" s="7"/>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A286" s="28"/>
+      <c r="B286" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="E285" s="7"/>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A286" s="42"/>
-      <c r="B286" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="C286" s="11"/>
       <c r="D286" s="11"/>
@@ -5147,31 +5150,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42FDF036-C785-4C62-8F8E-1B2A4FDE68FD}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
